--- a/data/trans_camb/P11_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 2,13</t>
+          <t>-7,34; 2,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,26</t>
+          <t>-5,51; 4,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 10,96</t>
+          <t>1,16; 10,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,18; 0,77</t>
+          <t>-12,02; 0,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 1,44</t>
+          <t>-10,62; 1,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 10,82</t>
+          <t>-1,19; 10,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 0,36</t>
+          <t>-7,62; -0,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 2,06</t>
+          <t>-5,57; 2,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 10,21</t>
+          <t>2,67; 10,03</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,46; 17,77</t>
+          <t>-41,92; 18,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,94; 33,6</t>
+          <t>-31,59; 37,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,86; 89,28</t>
+          <t>5,63; 78,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 4,56</t>
+          <t>-48,13; 3,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,74; 7,41</t>
+          <t>-41,38; 10,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 57,83</t>
+          <t>-4,72; 56,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,73; 2,31</t>
+          <t>-39,22; -1,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 13,36</t>
+          <t>-28,49; 14,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,83; 64,15</t>
+          <t>13,49; 66,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 9,78</t>
+          <t>-0,98; 10,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,07</t>
+          <t>-4,47; 5,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 16,24</t>
+          <t>6,03; 16,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 6,45</t>
+          <t>-4,98; 6,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 6,85</t>
+          <t>-4,39; 7,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 15,75</t>
+          <t>4,52; 15,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 6,22</t>
+          <t>-1,65; 6,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,67</t>
+          <t>-2,81; 4,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 14,21</t>
+          <t>6,85; 14,42</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 100,31</t>
+          <t>-6,76; 114,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 50,71</t>
+          <t>-30,99; 59,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,65; 175,33</t>
+          <t>38,55; 170,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 42,27</t>
+          <t>-23,7; 44,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,09; 43,34</t>
+          <t>-21,15; 47,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,62; 106,49</t>
+          <t>21,87; 108,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 45,29</t>
+          <t>-9,39; 47,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,91; 34,19</t>
+          <t>-17,16; 35,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,3; 112,08</t>
+          <t>39,15; 111,77</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 10,06</t>
+          <t>0,25; 10,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 7,2</t>
+          <t>-2,9; 6,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 14,05</t>
+          <t>-13,28; 14,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 11,45</t>
+          <t>-7,45; 11,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 8,16</t>
+          <t>-11,56; 9,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 25,31</t>
+          <t>6,72; 25,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 9,07</t>
+          <t>0,28; 9,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 5,76</t>
+          <t>-2,76; 5,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 15,69</t>
+          <t>-12,03; 15,2</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 63,0</t>
+          <t>1,1; 63,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 43,74</t>
+          <t>-13,52; 43,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-61,35; 78,55</t>
+          <t>-64,87; 86,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 46,7</t>
+          <t>-21,93; 44,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 32,65</t>
+          <t>-33,0; 38,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,44; 100,23</t>
+          <t>18,31; 104,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 48,14</t>
+          <t>0,47; 49,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,88; 31,22</t>
+          <t>-12,06; 30,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,88; 77,07</t>
+          <t>-53,84; 75,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 2,64</t>
+          <t>-4,08; 3,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,49</t>
+          <t>-4,04; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 11,82</t>
+          <t>4,45; 11,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 3,37</t>
+          <t>-6,15; 2,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 3,15</t>
+          <t>-6,56; 2,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,86; 47,37</t>
+          <t>6,97; 42,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 1,71</t>
+          <t>-3,48; 2,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,7</t>
+          <t>-3,61; 1,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,52; 31,02</t>
+          <t>7,6; 35,35</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 12,38</t>
+          <t>-17,13; 15,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 11,62</t>
+          <t>-16,91; 11,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17,36; 56,55</t>
+          <t>18,07; 54,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-20,05; 14,32</t>
+          <t>-21,14; 11,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 13,25</t>
+          <t>-22,5; 10,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,08; 195,68</t>
+          <t>26,43; 182,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 7,55</t>
+          <t>-13,71; 10,14</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 7,57</t>
+          <t>-14,44; 8,28</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,17; 134,28</t>
+          <t>30,88; 151,33</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,67</t>
+          <t>-7,84; 3,56</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 6,75</t>
+          <t>-4,39; 6,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,5; 17,17</t>
+          <t>5,03; 17,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,71; 15,88</t>
+          <t>5,81; 16,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,23</t>
+          <t>2,36; 12,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 20,31</t>
+          <t>1,63; 20,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,35</t>
+          <t>1,51; 9,46</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,96</t>
+          <t>0,71; 8,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,34; 17,14</t>
+          <t>4,36; 17,14</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 19,68</t>
+          <t>-30,49; 19,56</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 36,48</t>
+          <t>-16,61; 36,49</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18,45; 92,03</t>
+          <t>18,57; 91,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15,15; 61,6</t>
+          <t>18,9; 65,08</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>5,09; 47,5</t>
+          <t>7,31; 50,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,33; 77,82</t>
+          <t>7,18; 76,64</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,71; 39,48</t>
+          <t>5,05; 39,85</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,35; 33,36</t>
+          <t>2,6; 34,12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>21,69; 72,13</t>
+          <t>16,36; 71,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 5,31</t>
+          <t>-3,8; 4,91</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 2,47</t>
+          <t>-5,54; 2,39</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 13,18</t>
+          <t>-1,94; 12,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,92</t>
+          <t>-1,85; 6,1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 1,87</t>
+          <t>-6,21; 1,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,46; 9,13</t>
+          <t>0,77; 9,36</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 5,31</t>
+          <t>-1,83; 4,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 0,44</t>
+          <t>-5,83; 1,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 7,0</t>
+          <t>-0,69; 7,03</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 116,76</t>
+          <t>-43,05; 114,99</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-66,28; 57,79</t>
+          <t>-63,39; 51,55</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,34; 240,36</t>
+          <t>-28,62; 230,44</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 17,28</t>
+          <t>-4,81; 18,19</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 5,47</t>
+          <t>-16,63; 4,18</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,78; 26,98</t>
+          <t>1,83; 27,16</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 18,74</t>
+          <t>-6,04; 16,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-20,33; 1,28</t>
+          <t>-18,8; 3,52</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 23,75</t>
+          <t>-2,15; 24,4</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,47</t>
+          <t>-1,32; 2,69</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,3</t>
+          <t>-1,61; 2,28</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,68; 9,63</t>
+          <t>1,16; 9,81</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 4,11</t>
+          <t>-0,12; 4,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,64</t>
+          <t>-2,75; 1,89</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,0</t>
+          <t>6,69; 23,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,97</t>
+          <t>-0,05; 2,94</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,62</t>
+          <t>-1,5; 1,51</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,76; 15,15</t>
+          <t>6,05; 16,77</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 14,09</t>
+          <t>-6,95; 15,07</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 13,46</t>
+          <t>-8,39; 13,09</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3,84; 54,49</t>
+          <t>8,54; 56,07</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 14,63</t>
+          <t>-0,4; 14,88</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 5,75</t>
+          <t>-9,03; 6,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,39; 74,07</t>
+          <t>22,42; 79,43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 12,94</t>
+          <t>-0,17; 12,86</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 7,08</t>
+          <t>-6,13; 6,55</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>24,13; 64,31</t>
+          <t>25,26; 70,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P11_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P11_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,15</t>
+          <t>6,36</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,19</t>
+          <t>5,05</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>6,3</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 2,15</t>
+          <t>-7,64; 1,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 4,67</t>
+          <t>-5,43; 4,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,5</t>
+          <t>0,99; 10,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 0,49</t>
+          <t>-11,98; 0,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 1,68</t>
+          <t>-11,58; 1,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 10,52</t>
+          <t>-0,53; 11,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -0,26</t>
+          <t>-7,51; 0,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 2,3</t>
+          <t>-5,56; 1,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,03</t>
+          <t>2,78; 10,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 18,39</t>
+          <t>-42,67; 14,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 37,82</t>
+          <t>-31,34; 35,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 78,73</t>
+          <t>5,81; 89,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-48,13; 3,04</t>
+          <t>-48,26; 2,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,38; 10,06</t>
+          <t>-43,02; 11,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 56,06</t>
+          <t>-2,31; 60,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,22; -1,82</t>
+          <t>-37,22; 3,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 14,38</t>
+          <t>-28,36; 12,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 66,2</t>
+          <t>13,15; 65,32</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11,25</t>
+          <t>10,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,39</t>
+          <t>10,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,56</t>
+          <t>10,26</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 10,5</t>
+          <t>-0,77; 9,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 5,46</t>
+          <t>-4,01; 5,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,03; 16,52</t>
+          <t>5,1; 15,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 6,7</t>
+          <t>-5,2; 6,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 7,0</t>
+          <t>-5,46; 6,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,52; 15,95</t>
+          <t>5,49; 15,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 6,36</t>
+          <t>-2,07; 6,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 4,48</t>
+          <t>-2,99; 4,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 14,42</t>
+          <t>6,6; 14,05</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 114,62</t>
+          <t>-5,77; 101,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-30,99; 59,71</t>
+          <t>-27,94; 59,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,55; 170,43</t>
+          <t>34,16; 166,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 44,15</t>
+          <t>-25,59; 41,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 47,19</t>
+          <t>-26,11; 42,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,87; 108,46</t>
+          <t>23,75; 105,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,39; 47,59</t>
+          <t>-12,73; 46,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,16; 35,23</t>
+          <t>-17,75; 34,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39,15; 111,77</t>
+          <t>36,92; 106,71</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>11,52</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,1</t>
+          <t>14,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>13,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 10,02</t>
+          <t>0,58; 9,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 6,94</t>
+          <t>-2,67; 6,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 14,89</t>
+          <t>6,37; 16,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 11,22</t>
+          <t>-6,66; 11,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,56; 9,78</t>
+          <t>-10,7; 9,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 25,18</t>
+          <t>5,5; 25,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 9,18</t>
+          <t>0,15; 9,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,76</t>
+          <t>-3,05; 6,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 15,2</t>
+          <t>8,26; 18,0</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 63,02</t>
+          <t>2,37; 64,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 43,11</t>
+          <t>-13,18; 43,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 86,58</t>
+          <t>30,3; 108,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 44,83</t>
+          <t>-19,2; 46,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 38,72</t>
+          <t>-31,36; 36,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,31; 104,47</t>
+          <t>16,04; 107,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 49,1</t>
+          <t>0,72; 51,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 30,21</t>
+          <t>-13,51; 32,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-53,84; 75,73</t>
+          <t>35,65; 96,53</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,29</t>
+          <t>8,34</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,37</t>
+          <t>8,23</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 3,23</t>
+          <t>-4,17; 2,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,54</t>
+          <t>-4,23; 2,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 11,6</t>
+          <t>4,13; 11,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 2,74</t>
+          <t>-5,95; 3,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 2,55</t>
+          <t>-6,21; 2,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,97; 42,82</t>
+          <t>4,42; 12,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,31</t>
+          <t>-3,54; 2,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,85</t>
+          <t>-3,5; 1,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,6; 35,35</t>
+          <t>5,5; 11,22</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,13; 15,33</t>
+          <t>-16,8; 14,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 11,58</t>
+          <t>-17,29; 12,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18,07; 54,86</t>
+          <t>17,24; 54,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,14; 11,08</t>
+          <t>-21,16; 13,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,5; 10,64</t>
+          <t>-21,8; 12,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,43; 182,33</t>
+          <t>15,33; 52,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,71; 10,14</t>
+          <t>-13,95; 8,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 8,28</t>
+          <t>-13,84; 7,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,88; 151,33</t>
+          <t>21,19; 49,6</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,05</t>
+          <t>9,54</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,36</t>
+          <t>17,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12,65</t>
+          <t>14,08</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 3,56</t>
+          <t>-8,51; 3,12</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 6,72</t>
+          <t>-4,0; 6,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,03; 17,26</t>
+          <t>3,44; 15,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 16,46</t>
+          <t>5,03; 16,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,36; 12,73</t>
+          <t>2,21; 12,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 20,1</t>
+          <t>12,89; 22,23</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,51; 9,46</t>
+          <t>1,33; 9,2</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,71; 8,18</t>
+          <t>0,48; 7,94</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 17,14</t>
+          <t>10,45; 17,71</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>54,01%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 19,56</t>
+          <t>-32,35; 15,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 36,49</t>
+          <t>-15,49; 36,44</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18,57; 91,67</t>
+          <t>13,04; 83,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18,9; 65,08</t>
+          <t>15,53; 64,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,31; 50,0</t>
+          <t>7,22; 49,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,18; 76,64</t>
+          <t>40,23; 88,13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,05; 39,85</t>
+          <t>5,17; 38,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2,6; 34,12</t>
+          <t>1,88; 33,15</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>16,36; 71,7</t>
+          <t>37,02; 74,19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,09</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,91</t>
+          <t>-3,68; 4,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 2,39</t>
+          <t>-5,33; 2,63</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 12,96</t>
+          <t>-2,04; 11,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 6,1</t>
+          <t>-2,16; 5,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 1,51</t>
+          <t>-6,28; 1,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,77; 9,36</t>
+          <t>0,02; 8,09</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,89</t>
+          <t>-1,61; 5,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 1,0</t>
+          <t>-6,06; 0,72</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,03</t>
+          <t>-0,56; 6,96</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-43,05; 114,99</t>
+          <t>-43,52; 98,02</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 51,55</t>
+          <t>-62,35; 55,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 230,44</t>
+          <t>-26,9; 214,9</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 18,19</t>
+          <t>-5,9; 16,95</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-16,63; 4,18</t>
+          <t>-16,66; 5,76</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,83; 27,16</t>
+          <t>0,08; 24,07</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 16,72</t>
+          <t>-4,96; 18,36</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 3,52</t>
+          <t>-19,12; 2,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 24,4</t>
+          <t>-1,86; 24,46</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,87</t>
+          <t>8,47</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,27</t>
+          <t>8,13</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>8,36</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 2,69</t>
+          <t>-1,23; 2,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,28</t>
+          <t>-1,65; 2,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,16; 9,81</t>
+          <t>6,41; 10,67</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 4,18</t>
+          <t>-0,02; 4,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 1,89</t>
+          <t>-2,68; 1,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,69; 23,13</t>
+          <t>5,75; 10,07</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,94</t>
+          <t>-0,02; 3,02</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,51</t>
+          <t>-1,38; 1,48</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6,05; 16,77</t>
+          <t>6,99; 9,86</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 15,07</t>
+          <t>-6,62; 15,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 13,09</t>
+          <t>-8,51; 14,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8,54; 56,07</t>
+          <t>33,56; 62,1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 14,88</t>
+          <t>-0,07; 15,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 6,73</t>
+          <t>-8,86; 5,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,42; 79,43</t>
+          <t>18,89; 35,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 12,86</t>
+          <t>-0,08; 13,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 6,55</t>
+          <t>-5,7; 6,43</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>25,26; 70,75</t>
+          <t>28,5; 42,81</t>
         </is>
       </c>
     </row>
